--- a/artfynd/A 47462-2024 artfynd.xlsx
+++ b/artfynd/A 47462-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136041986</v>
       </c>
       <c r="B3" t="n">
-        <v>98770</v>
+        <v>98773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136041995</v>
       </c>
       <c r="B4" t="n">
-        <v>103919</v>
+        <v>103922</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47462-2024 artfynd.xlsx
+++ b/artfynd/A 47462-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136041986</v>
       </c>
       <c r="B3" t="n">
-        <v>98773</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136041995</v>
       </c>
       <c r="B4" t="n">
-        <v>103922</v>
+        <v>103923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
